--- a/data/trans_orig/KIDM_C_3_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_3_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35834</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30516</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>69577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74400</t>
+          <t>74401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>26049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49886</t>
+          <t>50245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45738</t>
+          <t>45744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50510</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72581</t>
+          <t>72478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78791</t>
+          <t>78771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>14222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75621</t>
+          <t>75418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83092</t>
+          <t>83155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75418</t>
+          <t>74999</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80765</t>
+          <t>80923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153721</t>
+          <t>153191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162694</t>
+          <t>162682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>41108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>46183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54212</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60703</t>
+          <t>60667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97837</t>
+          <t>97146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105954</t>
+          <t>105716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33689</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65601</t>
+          <t>65384</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>19478</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32757</t>
+          <t>31936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245953</t>
+          <t>245611</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>257254</t>
+          <t>256703</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>274246</t>
+          <t>274664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285345</t>
+          <t>284989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>524136</t>
+          <t>524957</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>540068</t>
+          <t>540165</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29860</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>35614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25658</t>
+          <t>25404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58157</t>
+          <t>57274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66609</t>
+          <t>66552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29215</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24968</t>
+          <t>25557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32025</t>
+          <t>32050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50281</t>
+          <t>49779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60047</t>
+          <t>60083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31403</t>
+          <t>31918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>39614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23661</t>
+          <t>23797</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>29488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57736</t>
+          <t>57802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67595</t>
+          <t>67562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25381</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37220</t>
+          <t>37942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59202</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71892</t>
+          <t>71814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81629</t>
+          <t>81604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91634</t>
+          <t>91649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145087</t>
+          <t>144365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161772</t>
+          <t>160493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60533</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69849</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57448</t>
+          <t>57631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66038</t>
+          <t>65969</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121968</t>
+          <t>121899</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134569</t>
+          <t>134137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18398</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34772</t>
+          <t>34786</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51479</t>
+          <t>50919</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57574</t>
+          <t>57532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>35853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>56448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>42684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65074</t>
+          <t>66178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92959</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238858</t>
+          <t>239471</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259207</t>
+          <t>260066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>260599</t>
+          <t>260246</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>278857</t>
+          <t>277704</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>505890</t>
+          <t>505403</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>533775</t>
+          <t>532671</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,95%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>26376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31897</t>
+          <t>31864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24703</t>
+          <t>24580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>33313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53572</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63838</t>
+          <t>64242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36167</t>
+          <t>36112</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45017</t>
+          <t>45245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42606</t>
+          <t>42626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47153</t>
+          <t>47155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82004</t>
+          <t>81904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91967</t>
+          <t>91944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>37891</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57311</t>
+          <t>56766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64878</t>
+          <t>64823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13814</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>21759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97605</t>
+          <t>98151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107104</t>
+          <t>107183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86468</t>
+          <t>85593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95160</t>
+          <t>95584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188047</t>
+          <t>188333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201043</t>
+          <t>201042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24535</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61097</t>
+          <t>61666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70436</t>
+          <t>70400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54246</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64239</t>
+          <t>64385</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119736</t>
+          <t>120311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133415</t>
+          <t>132560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26830</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32724</t>
+          <t>32736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31753</t>
+          <t>31672</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>36494</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60908</t>
+          <t>61166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>68523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43112</t>
+          <t>45186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50028</t>
+          <t>50201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75631</t>
+          <t>76571</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>289704</t>
+          <t>290807</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>307125</t>
+          <t>307981</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288207</t>
+          <t>286133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306314</t>
+          <t>305542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>583729</t>
+          <t>582789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>609332</t>
+          <t>609159</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66347</t>
+          <t>66407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55626</t>
+          <t>55353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>10878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38265</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>245</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11431</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58477</t>
+          <t>58659</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66734</t>
+          <t>66910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64655</t>
+          <t>65088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126511</t>
+          <t>127297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135928</t>
+          <t>136222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54430</t>
+          <t>54438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86229</t>
+          <t>86459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94154</t>
+          <t>94069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>19903</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193056</t>
+          <t>193318</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203578</t>
+          <t>203675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>255320</t>
+          <t>255221</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>263877</t>
+          <t>263919</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>452410</t>
+          <t>453046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>465139</t>
+          <t>465050</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
